--- a/Клиенты/ProfiMet/Статистика/dashboard_sources_2026-08-01_2026-10-19.xlsx
+++ b/Клиенты/ProfiMet/Статистика/dashboard_sources_2026-08-01_2026-10-19.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="6">
@@ -564,6 +564,18 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Режим подсчёта конверсий и звонков</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Наш (60 дней, формы из CRM)</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
@@ -658,7 +670,7 @@
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9)</f>
+        <f>IF(LEFT($B$7,3)="Как",SUMIFS('Данные'!$I:$I,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9),SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9))</f>
         <v/>
       </c>
       <c r="H9" s="9">
@@ -670,7 +682,7 @@
         <v/>
       </c>
       <c r="J9" s="8">
-        <f>SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9)</f>
+        <f>IF(LEFT($B$7,3)="Как",SUMIFS('Данные'!$J:$J,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9),SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A9))</f>
         <v/>
       </c>
       <c r="K9" s="8">
@@ -713,7 +725,7 @@
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10)</f>
+        <f>IF(LEFT($B$7,3)="Как",SUMIFS('Данные'!$I:$I,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10),SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10))</f>
         <v/>
       </c>
       <c r="H10" s="9">
@@ -725,7 +737,7 @@
         <v/>
       </c>
       <c r="J10" s="8">
-        <f>SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10)</f>
+        <f>IF(LEFT($B$7,3)="Как",SUMIFS('Данные'!$J:$J,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10),SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A10))</f>
         <v/>
       </c>
       <c r="K10" s="8">
@@ -773,7 +785,7 @@
         </is>
       </c>
       <c r="G11" s="8">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A11)</f>
+        <f>IF(LEFT($B$7,3)="Как",SUMIFS('Данные'!$I:$I,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A11),SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A11))</f>
         <v/>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -994,26 +1006,29 @@
     </row>
     <row r="16">
       <c r="A16">
-        <f>"Телефон: новых обращений "&amp;SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A12)&amp;" (из них звонков "&amp;SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A12)&amp;") — в «Конверсии» и «Звонки» не включены"</f>
+        <f>IF(LEFT($B$7,3)="Как","Режим «как у клиента»: звонки — первый звонок номера за всю историю Ringostat; формы — сеансы GA4 form_submit по источнику сеанса; Телефон и Прочее без конверсий. Продажи — по нашему правилу (выгрузка CRM) в обоих режимах.","Телефон: новых обращений "&amp;SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A12)&amp;" (из них звонков "&amp;SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A12)&amp;") — в «Конверсии» и «Звонки» не включены")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>"Нет метки: из "&amp;G11&amp;" конверсий звонков "&amp;SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A11)&amp;" — в колонке «Звонки» не показаны"</f>
+        <f>IF(LEFT($B$7,3)="Как","","Нет метки: из "&amp;G11&amp;" конверсий звонков "&amp;SUMIFS('Данные'!$G:$G,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A11)&amp;" — в колонке «Звонки» не показаны")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>"Прочее: новых обращений "&amp;SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A13)&amp;" — в «Конверсии» и «Звонки» не включены"</f>
+        <f>IF(LEFT($B$7,3)="Как","","Прочее: новых обращений "&amp;SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$B$3,'Данные'!$A:$A,"&lt;="&amp;$B$4,'Данные'!$B:$B,$A13)&amp;" — в «Конверсии» и «Звонки» не включены")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>='Списки'!$A$2:$A$25</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Наш (60 дней, формы из CRM),Как у клиента (звонки за всю историю, формы GA4)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1026,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H401"/>
+  <dimension ref="A1:J401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1034,9 +1049,11 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,7 +1084,7 @@
       </c>
       <c r="F1" s="13" t="inlineStr">
         <is>
-          <t>Конверсии (новые обращения)</t>
+          <t>Конверсии (наш режим: новые обращения CRM)</t>
         </is>
       </c>
       <c r="G1" s="13" t="inlineStr">
@@ -1078,6 +1095,16 @@
       <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Продажи</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Конверсии (как у клиента: звонки + формы GA4)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>из них звонки (первый звонок за всю историю)</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1135,12 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1136,6 +1169,12 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1164,6 +1203,12 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1192,6 +1237,12 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1220,6 +1271,12 @@
       <c r="H6" t="n">
         <v>0</v>
       </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1248,6 +1305,12 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1276,6 +1339,12 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1304,6 +1373,12 @@
       <c r="H9" t="n">
         <v>0</v>
       </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1332,6 +1407,12 @@
       <c r="H10" t="n">
         <v>0</v>
       </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1360,6 +1441,12 @@
       <c r="H11" t="n">
         <v>0</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1388,6 +1475,12 @@
       <c r="H12" t="n">
         <v>0</v>
       </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1416,6 +1509,12 @@
       <c r="H13" t="n">
         <v>0</v>
       </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1444,6 +1543,12 @@
       <c r="H14" t="n">
         <v>0</v>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1472,6 +1577,12 @@
       <c r="H15" t="n">
         <v>0</v>
       </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1500,6 +1611,12 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1528,6 +1645,12 @@
       <c r="H17" t="n">
         <v>1</v>
       </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1556,6 +1679,12 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1584,6 +1713,12 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1612,6 +1747,12 @@
       <c r="H20" t="n">
         <v>0</v>
       </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1640,6 +1781,12 @@
       <c r="H21" t="n">
         <v>0</v>
       </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1668,6 +1815,12 @@
       <c r="H22" t="n">
         <v>1</v>
       </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1696,6 +1849,12 @@
       <c r="H23" t="n">
         <v>1</v>
       </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1724,6 +1883,12 @@
       <c r="H24" t="n">
         <v>0</v>
       </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1752,6 +1917,12 @@
       <c r="H25" t="n">
         <v>0</v>
       </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1780,6 +1951,12 @@
       <c r="H26" t="n">
         <v>0</v>
       </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1808,6 +1985,12 @@
       <c r="H27" t="n">
         <v>0</v>
       </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1836,6 +2019,12 @@
       <c r="H28" t="n">
         <v>0</v>
       </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1864,6 +2053,12 @@
       <c r="H29" t="n">
         <v>0</v>
       </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1892,6 +2087,12 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1920,6 +2121,12 @@
       <c r="H31" t="n">
         <v>0</v>
       </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1948,6 +2155,12 @@
       <c r="H32" t="n">
         <v>2</v>
       </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1976,6 +2189,12 @@
       <c r="H33" t="n">
         <v>1</v>
       </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2004,6 +2223,12 @@
       <c r="H34" t="n">
         <v>1</v>
       </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2032,6 +2257,12 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2060,6 +2291,12 @@
       <c r="H36" t="n">
         <v>0</v>
       </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2088,6 +2325,12 @@
       <c r="H37" t="n">
         <v>0</v>
       </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2116,6 +2359,12 @@
       <c r="H38" t="n">
         <v>0</v>
       </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2144,6 +2393,12 @@
       <c r="H39" t="n">
         <v>0</v>
       </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2172,6 +2427,12 @@
       <c r="H40" t="n">
         <v>0</v>
       </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2200,6 +2461,12 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2228,6 +2495,12 @@
       <c r="H42" t="n">
         <v>0</v>
       </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2256,6 +2529,12 @@
       <c r="H43" t="n">
         <v>0</v>
       </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2284,6 +2563,12 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2312,6 +2597,12 @@
       <c r="H45" t="n">
         <v>0</v>
       </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2340,6 +2631,12 @@
       <c r="H46" t="n">
         <v>0</v>
       </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2368,6 +2665,12 @@
       <c r="H47" t="n">
         <v>2</v>
       </c>
+      <c r="I47" t="n">
+        <v>4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2396,6 +2699,12 @@
       <c r="H48" t="n">
         <v>2</v>
       </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2424,6 +2733,12 @@
       <c r="H49" t="n">
         <v>1</v>
       </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2452,6 +2767,12 @@
       <c r="H50" t="n">
         <v>1</v>
       </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2480,6 +2801,12 @@
       <c r="H51" t="n">
         <v>0</v>
       </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2508,6 +2835,12 @@
       <c r="H52" t="n">
         <v>0</v>
       </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2536,6 +2869,12 @@
       <c r="H53" t="n">
         <v>2</v>
       </c>
+      <c r="I53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2564,6 +2903,12 @@
       <c r="H54" t="n">
         <v>2</v>
       </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2592,6 +2937,12 @@
       <c r="H55" t="n">
         <v>1</v>
       </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2620,6 +2971,12 @@
       <c r="H56" t="n">
         <v>0</v>
       </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2648,6 +3005,12 @@
       <c r="H57" t="n">
         <v>2</v>
       </c>
+      <c r="I57" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2676,6 +3039,12 @@
       <c r="H58" t="n">
         <v>2</v>
       </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -2704,6 +3073,12 @@
       <c r="H59" t="n">
         <v>0</v>
       </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -2732,6 +3107,12 @@
       <c r="H60" t="n">
         <v>0</v>
       </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -2760,6 +3141,12 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -2788,6 +3175,12 @@
       <c r="H62" t="n">
         <v>3</v>
       </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -2816,6 +3209,12 @@
       <c r="H63" t="n">
         <v>0</v>
       </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -2844,6 +3243,12 @@
       <c r="H64" t="n">
         <v>0</v>
       </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -2872,6 +3277,12 @@
       <c r="H65" t="n">
         <v>0</v>
       </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -2900,6 +3311,12 @@
       <c r="H66" t="n">
         <v>0</v>
       </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -2928,6 +3345,12 @@
       <c r="H67" t="n">
         <v>1</v>
       </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -2956,6 +3379,12 @@
       <c r="H68" t="n">
         <v>0</v>
       </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -2984,6 +3413,12 @@
       <c r="H69" t="n">
         <v>0</v>
       </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -3012,6 +3447,12 @@
       <c r="H70" t="n">
         <v>1</v>
       </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -3040,6 +3481,12 @@
       <c r="H71" t="n">
         <v>0</v>
       </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -3068,6 +3515,12 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -3096,6 +3549,12 @@
       <c r="H73" t="n">
         <v>0</v>
       </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -3124,6 +3583,12 @@
       <c r="H74" t="n">
         <v>0</v>
       </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -3152,6 +3617,12 @@
       <c r="H75" t="n">
         <v>0</v>
       </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -3180,6 +3651,12 @@
       <c r="H76" t="n">
         <v>0</v>
       </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -3208,6 +3685,12 @@
       <c r="H77" t="n">
         <v>0</v>
       </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -3236,6 +3719,12 @@
       <c r="H78" t="n">
         <v>0</v>
       </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -3264,6 +3753,12 @@
       <c r="H79" t="n">
         <v>0</v>
       </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -3292,6 +3787,12 @@
       <c r="H80" t="n">
         <v>0</v>
       </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -3320,6 +3821,12 @@
       <c r="H81" t="n">
         <v>0</v>
       </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -3348,6 +3855,12 @@
       <c r="H82" t="n">
         <v>1</v>
       </c>
+      <c r="I82" t="n">
+        <v>4</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -3376,6 +3889,12 @@
       <c r="H83" t="n">
         <v>1</v>
       </c>
+      <c r="I83" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -3404,6 +3923,12 @@
       <c r="H84" t="n">
         <v>0</v>
       </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -3432,6 +3957,12 @@
       <c r="H85" t="n">
         <v>2</v>
       </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -3460,6 +3991,12 @@
       <c r="H86" t="n">
         <v>0</v>
       </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -3488,6 +4025,12 @@
       <c r="H87" t="n">
         <v>5</v>
       </c>
+      <c r="I87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -3516,6 +4059,12 @@
       <c r="H88" t="n">
         <v>0</v>
       </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -3544,6 +4093,12 @@
       <c r="H89" t="n">
         <v>0</v>
       </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -3572,6 +4127,12 @@
       <c r="H90" t="n">
         <v>0</v>
       </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -3600,6 +4161,12 @@
       <c r="H91" t="n">
         <v>0</v>
       </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -3628,6 +4195,12 @@
       <c r="H92" t="n">
         <v>0</v>
       </c>
+      <c r="I92" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -3656,6 +4229,12 @@
       <c r="H93" t="n">
         <v>0</v>
       </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -3684,6 +4263,12 @@
       <c r="H94" t="n">
         <v>0</v>
       </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -3712,6 +4297,12 @@
       <c r="H95" t="n">
         <v>1</v>
       </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -3740,6 +4331,12 @@
       <c r="H96" t="n">
         <v>0</v>
       </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -3768,6 +4365,12 @@
       <c r="H97" t="n">
         <v>1</v>
       </c>
+      <c r="I97" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -3796,6 +4399,12 @@
       <c r="H98" t="n">
         <v>0</v>
       </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -3824,6 +4433,12 @@
       <c r="H99" t="n">
         <v>0</v>
       </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -3852,6 +4467,12 @@
       <c r="H100" t="n">
         <v>0</v>
       </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -3880,6 +4501,12 @@
       <c r="H101" t="n">
         <v>0</v>
       </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -3908,6 +4535,12 @@
       <c r="H102" t="n">
         <v>1</v>
       </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -3936,6 +4569,12 @@
       <c r="H103" t="n">
         <v>3</v>
       </c>
+      <c r="I103" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -3964,6 +4603,12 @@
       <c r="H104" t="n">
         <v>0</v>
       </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -3992,6 +4637,12 @@
       <c r="H105" t="n">
         <v>0</v>
       </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -4020,6 +4671,12 @@
       <c r="H106" t="n">
         <v>0</v>
       </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -4048,6 +4705,12 @@
       <c r="H107" t="n">
         <v>0</v>
       </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -4076,6 +4739,12 @@
       <c r="H108" t="n">
         <v>0</v>
       </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -4104,6 +4773,12 @@
       <c r="H109" t="n">
         <v>0</v>
       </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -4132,6 +4807,12 @@
       <c r="H110" t="n">
         <v>0</v>
       </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -4160,6 +4841,12 @@
       <c r="H111" t="n">
         <v>0</v>
       </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -4188,6 +4875,12 @@
       <c r="H112" t="n">
         <v>0</v>
       </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -4216,6 +4909,12 @@
       <c r="H113" t="n">
         <v>0</v>
       </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n">
@@ -4244,6 +4943,12 @@
       <c r="H114" t="n">
         <v>0</v>
       </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -4272,6 +4977,12 @@
       <c r="H115" t="n">
         <v>0</v>
       </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="n">
@@ -4300,6 +5011,12 @@
       <c r="H116" t="n">
         <v>0</v>
       </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -4328,6 +5045,12 @@
       <c r="H117" t="n">
         <v>4</v>
       </c>
+      <c r="I117" t="n">
+        <v>13</v>
+      </c>
+      <c r="J117" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -4356,6 +5079,12 @@
       <c r="H118" t="n">
         <v>1</v>
       </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -4384,6 +5113,12 @@
       <c r="H119" t="n">
         <v>0</v>
       </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="n">
@@ -4412,6 +5147,12 @@
       <c r="H120" t="n">
         <v>2</v>
       </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -4440,6 +5181,12 @@
       <c r="H121" t="n">
         <v>0</v>
       </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -4468,6 +5215,12 @@
       <c r="H122" t="n">
         <v>8</v>
       </c>
+      <c r="I122" t="n">
+        <v>20</v>
+      </c>
+      <c r="J122" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="n">
@@ -4496,6 +5249,12 @@
       <c r="H123" t="n">
         <v>0</v>
       </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
@@ -4524,6 +5283,12 @@
       <c r="H124" t="n">
         <v>0</v>
       </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -4552,6 +5317,12 @@
       <c r="H125" t="n">
         <v>2</v>
       </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n">
@@ -4580,6 +5351,12 @@
       <c r="H126" t="n">
         <v>0</v>
       </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -4608,6 +5385,12 @@
       <c r="H127" t="n">
         <v>3</v>
       </c>
+      <c r="I127" t="n">
+        <v>5</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -4636,6 +5419,12 @@
       <c r="H128" t="n">
         <v>0</v>
       </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -4664,6 +5453,12 @@
       <c r="H129" t="n">
         <v>1</v>
       </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
@@ -4692,6 +5487,12 @@
       <c r="H130" t="n">
         <v>0</v>
       </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -4720,6 +5521,12 @@
       <c r="H131" t="n">
         <v>0</v>
       </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="n">
@@ -4748,6 +5555,12 @@
       <c r="H132" t="n">
         <v>2</v>
       </c>
+      <c r="I132" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -4776,6 +5589,12 @@
       <c r="H133" t="n">
         <v>0</v>
       </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="n">
@@ -4804,6 +5623,12 @@
       <c r="H134" t="n">
         <v>3</v>
       </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -4832,6 +5657,12 @@
       <c r="H135" t="n">
         <v>0</v>
       </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -4860,6 +5691,12 @@
       <c r="H136" t="n">
         <v>0</v>
       </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -4888,6 +5725,12 @@
       <c r="H137" t="n">
         <v>1</v>
       </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
@@ -4916,6 +5759,12 @@
       <c r="H138" t="n">
         <v>0</v>
       </c>
+      <c r="I138" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -4944,6 +5793,12 @@
       <c r="H139" t="n">
         <v>1</v>
       </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
@@ -4972,6 +5827,12 @@
       <c r="H140" t="n">
         <v>2</v>
       </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="n">
@@ -5000,6 +5861,12 @@
       <c r="H141" t="n">
         <v>0</v>
       </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -5028,6 +5895,12 @@
       <c r="H142" t="n">
         <v>0</v>
       </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n">
@@ -5056,6 +5929,12 @@
       <c r="H143" t="n">
         <v>0</v>
       </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n">
@@ -5084,6 +5963,12 @@
       <c r="H144" t="n">
         <v>0</v>
       </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -5112,6 +5997,12 @@
       <c r="H145" t="n">
         <v>0</v>
       </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n">
@@ -5140,6 +6031,12 @@
       <c r="H146" t="n">
         <v>0</v>
       </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -5168,6 +6065,12 @@
       <c r="H147" t="n">
         <v>0</v>
       </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
@@ -5196,6 +6099,12 @@
       <c r="H148" t="n">
         <v>0</v>
       </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -5224,6 +6133,12 @@
       <c r="H149" t="n">
         <v>0</v>
       </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -5252,6 +6167,12 @@
       <c r="H150" t="n">
         <v>0</v>
       </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -5280,6 +6201,12 @@
       <c r="H151" t="n">
         <v>0</v>
       </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -5308,6 +6235,12 @@
       <c r="H152" t="n">
         <v>2</v>
       </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -5336,6 +6269,12 @@
       <c r="H153" t="n">
         <v>1</v>
       </c>
+      <c r="I153" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n">
@@ -5364,6 +6303,12 @@
       <c r="H154" t="n">
         <v>1</v>
       </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -5392,6 +6337,12 @@
       <c r="H155" t="n">
         <v>1</v>
       </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -5420,6 +6371,12 @@
       <c r="H156" t="n">
         <v>0</v>
       </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -5448,6 +6405,12 @@
       <c r="H157" t="n">
         <v>3</v>
       </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -5476,6 +6439,12 @@
       <c r="H158" t="n">
         <v>1</v>
       </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -5504,6 +6473,12 @@
       <c r="H159" t="n">
         <v>1</v>
       </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n">
@@ -5532,6 +6507,12 @@
       <c r="H160" t="n">
         <v>1</v>
       </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -5560,6 +6541,12 @@
       <c r="H161" t="n">
         <v>0</v>
       </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
@@ -5588,6 +6575,12 @@
       <c r="H162" t="n">
         <v>1</v>
       </c>
+      <c r="I162" t="n">
+        <v>6</v>
+      </c>
+      <c r="J162" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -5616,6 +6609,12 @@
       <c r="H163" t="n">
         <v>0</v>
       </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
@@ -5644,6 +6643,12 @@
       <c r="H164" t="n">
         <v>0</v>
       </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -5672,6 +6677,12 @@
       <c r="H165" t="n">
         <v>2</v>
       </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -5700,6 +6711,12 @@
       <c r="H166" t="n">
         <v>0</v>
       </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -5728,6 +6745,12 @@
       <c r="H167" t="n">
         <v>2</v>
       </c>
+      <c r="I167" t="n">
+        <v>2</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
@@ -5756,6 +6779,12 @@
       <c r="H168" t="n">
         <v>2</v>
       </c>
+      <c r="I168" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -5784,6 +6813,12 @@
       <c r="H169" t="n">
         <v>1</v>
       </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
@@ -5812,6 +6847,12 @@
       <c r="H170" t="n">
         <v>1</v>
       </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -5840,6 +6881,12 @@
       <c r="H171" t="n">
         <v>0</v>
       </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -5868,6 +6915,12 @@
       <c r="H172" t="n">
         <v>2</v>
       </c>
+      <c r="I172" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -5896,6 +6949,12 @@
       <c r="H173" t="n">
         <v>1</v>
       </c>
+      <c r="I173" t="n">
+        <v>2</v>
+      </c>
+      <c r="J173" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
@@ -5924,6 +6983,12 @@
       <c r="H174" t="n">
         <v>0</v>
       </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -5952,6 +7017,12 @@
       <c r="H175" t="n">
         <v>0</v>
       </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
@@ -5980,6 +7051,12 @@
       <c r="H176" t="n">
         <v>0</v>
       </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -6008,6 +7085,12 @@
       <c r="H177" t="n">
         <v>0</v>
       </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
@@ -6036,6 +7119,12 @@
       <c r="H178" t="n">
         <v>0</v>
       </c>
+      <c r="I178" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
@@ -6064,6 +7153,12 @@
       <c r="H179" t="n">
         <v>0</v>
       </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
@@ -6092,6 +7187,12 @@
       <c r="H180" t="n">
         <v>0</v>
       </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -6120,6 +7221,12 @@
       <c r="H181" t="n">
         <v>0</v>
       </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n">
@@ -6148,6 +7255,12 @@
       <c r="H182" t="n">
         <v>0</v>
       </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
@@ -6176,6 +7289,12 @@
       <c r="H183" t="n">
         <v>0</v>
       </c>
+      <c r="I183" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n">
@@ -6204,6 +7323,12 @@
       <c r="H184" t="n">
         <v>0</v>
       </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
@@ -6232,6 +7357,12 @@
       <c r="H185" t="n">
         <v>0</v>
       </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="n">
@@ -6260,6 +7391,12 @@
       <c r="H186" t="n">
         <v>0</v>
       </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -6288,6 +7425,12 @@
       <c r="H187" t="n">
         <v>5</v>
       </c>
+      <c r="I187" t="n">
+        <v>11</v>
+      </c>
+      <c r="J187" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n">
@@ -6316,6 +7459,12 @@
       <c r="H188" t="n">
         <v>2</v>
       </c>
+      <c r="I188" t="n">
+        <v>2</v>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n">
@@ -6344,6 +7493,12 @@
       <c r="H189" t="n">
         <v>1</v>
       </c>
+      <c r="I189" t="n">
+        <v>4</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n">
@@ -6372,6 +7527,12 @@
       <c r="H190" t="n">
         <v>4</v>
       </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -6400,6 +7561,12 @@
       <c r="H191" t="n">
         <v>0</v>
       </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n">
@@ -6428,6 +7595,12 @@
       <c r="H192" t="n">
         <v>6</v>
       </c>
+      <c r="I192" t="n">
+        <v>12</v>
+      </c>
+      <c r="J192" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -6456,6 +7629,12 @@
       <c r="H193" t="n">
         <v>1</v>
       </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
@@ -6484,6 +7663,12 @@
       <c r="H194" t="n">
         <v>2</v>
       </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -6512,6 +7697,12 @@
       <c r="H195" t="n">
         <v>1</v>
       </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
@@ -6540,6 +7731,12 @@
       <c r="H196" t="n">
         <v>0</v>
       </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
@@ -6568,6 +7765,12 @@
       <c r="H197" t="n">
         <v>1</v>
       </c>
+      <c r="I197" t="n">
+        <v>5</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n">
@@ -6596,6 +7799,12 @@
       <c r="H198" t="n">
         <v>2</v>
       </c>
+      <c r="I198" t="n">
+        <v>3</v>
+      </c>
+      <c r="J198" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
@@ -6624,6 +7833,12 @@
       <c r="H199" t="n">
         <v>2</v>
       </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
@@ -6652,6 +7867,12 @@
       <c r="H200" t="n">
         <v>2</v>
       </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -6680,6 +7901,12 @@
       <c r="H201" t="n">
         <v>0</v>
       </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
@@ -6708,6 +7935,12 @@
       <c r="H202" t="n">
         <v>3</v>
       </c>
+      <c r="I202" t="n">
+        <v>5</v>
+      </c>
+      <c r="J202" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
@@ -6736,6 +7969,12 @@
       <c r="H203" t="n">
         <v>1</v>
       </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n">
@@ -6764,6 +8003,12 @@
       <c r="H204" t="n">
         <v>0</v>
       </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
@@ -6792,6 +8037,12 @@
       <c r="H205" t="n">
         <v>1</v>
       </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
@@ -6820,6 +8071,12 @@
       <c r="H206" t="n">
         <v>0</v>
       </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="n">
@@ -6848,6 +8105,12 @@
       <c r="H207" t="n">
         <v>2</v>
       </c>
+      <c r="I207" t="n">
+        <v>3</v>
+      </c>
+      <c r="J207" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
@@ -6876,6 +8139,12 @@
       <c r="H208" t="n">
         <v>0</v>
       </c>
+      <c r="I208" t="n">
+        <v>2</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n">
@@ -6904,6 +8173,12 @@
       <c r="H209" t="n">
         <v>0</v>
       </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n">
@@ -6932,6 +8207,12 @@
       <c r="H210" t="n">
         <v>1</v>
       </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
@@ -6960,6 +8241,12 @@
       <c r="H211" t="n">
         <v>0</v>
       </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n">
@@ -6988,6 +8275,12 @@
       <c r="H212" t="n">
         <v>0</v>
       </c>
+      <c r="I212" t="n">
+        <v>2</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
@@ -7016,6 +8309,12 @@
       <c r="H213" t="n">
         <v>0</v>
       </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="n">
@@ -7044,6 +8343,12 @@
       <c r="H214" t="n">
         <v>0</v>
       </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
@@ -7072,6 +8377,12 @@
       <c r="H215" t="n">
         <v>0</v>
       </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="n">
@@ -7100,6 +8411,12 @@
       <c r="H216" t="n">
         <v>0</v>
       </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n">
@@ -7128,6 +8445,12 @@
       <c r="H217" t="n">
         <v>0</v>
       </c>
+      <c r="I217" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="n">
@@ -7156,6 +8479,12 @@
       <c r="H218" t="n">
         <v>0</v>
       </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
@@ -7184,6 +8513,12 @@
       <c r="H219" t="n">
         <v>0</v>
       </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n">
@@ -7212,6 +8547,12 @@
       <c r="H220" t="n">
         <v>0</v>
       </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="n">
@@ -7240,6 +8581,12 @@
       <c r="H221" t="n">
         <v>0</v>
       </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
@@ -7268,6 +8615,12 @@
       <c r="H222" t="n">
         <v>5</v>
       </c>
+      <c r="I222" t="n">
+        <v>11</v>
+      </c>
+      <c r="J222" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
@@ -7296,6 +8649,12 @@
       <c r="H223" t="n">
         <v>1</v>
       </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n">
@@ -7324,6 +8683,12 @@
       <c r="H224" t="n">
         <v>5</v>
       </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
@@ -7352,6 +8717,12 @@
       <c r="H225" t="n">
         <v>2</v>
       </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="n">
@@ -7380,6 +8751,12 @@
       <c r="H226" t="n">
         <v>0</v>
       </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
@@ -7408,6 +8785,12 @@
       <c r="H227" t="n">
         <v>2</v>
       </c>
+      <c r="I227" t="n">
+        <v>4</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n">
@@ -7436,6 +8819,12 @@
       <c r="H228" t="n">
         <v>1</v>
       </c>
+      <c r="I228" t="n">
+        <v>2</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
@@ -7464,6 +8853,12 @@
       <c r="H229" t="n">
         <v>0</v>
       </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n">
@@ -7492,6 +8887,12 @@
       <c r="H230" t="n">
         <v>3</v>
       </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
@@ -7520,6 +8921,12 @@
       <c r="H231" t="n">
         <v>0</v>
       </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="n">
@@ -7548,6 +8955,12 @@
       <c r="H232" t="n">
         <v>2</v>
       </c>
+      <c r="I232" t="n">
+        <v>5</v>
+      </c>
+      <c r="J232" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
@@ -7576,6 +8989,12 @@
       <c r="H233" t="n">
         <v>0</v>
       </c>
+      <c r="I233" t="n">
+        <v>4</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="n">
@@ -7604,6 +9023,12 @@
       <c r="H234" t="n">
         <v>1</v>
       </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
@@ -7632,6 +9057,12 @@
       <c r="H235" t="n">
         <v>1</v>
       </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="n">
@@ -7660,6 +9091,12 @@
       <c r="H236" t="n">
         <v>0</v>
       </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
@@ -7688,6 +9125,12 @@
       <c r="H237" t="n">
         <v>5</v>
       </c>
+      <c r="I237" t="n">
+        <v>9</v>
+      </c>
+      <c r="J237" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="4" t="n">
@@ -7716,6 +9159,12 @@
       <c r="H238" t="n">
         <v>3</v>
       </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
@@ -7744,6 +9193,12 @@
       <c r="H239" t="n">
         <v>2</v>
       </c>
+      <c r="I239" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n">
@@ -7772,6 +9227,12 @@
       <c r="H240" t="n">
         <v>2</v>
       </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n">
@@ -7800,6 +9261,12 @@
       <c r="H241" t="n">
         <v>0</v>
       </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="n">
@@ -7828,6 +9295,12 @@
       <c r="H242" t="n">
         <v>1</v>
       </c>
+      <c r="I242" t="n">
+        <v>3</v>
+      </c>
+      <c r="J242" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n">
@@ -7856,6 +9329,12 @@
       <c r="H243" t="n">
         <v>0</v>
       </c>
+      <c r="I243" t="n">
+        <v>1</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n">
@@ -7884,6 +9363,12 @@
       <c r="H244" t="n">
         <v>1</v>
       </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n">
@@ -7912,6 +9397,12 @@
       <c r="H245" t="n">
         <v>2</v>
       </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n">
@@ -7940,6 +9431,12 @@
       <c r="H246" t="n">
         <v>0</v>
       </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n">
@@ -7968,6 +9465,12 @@
       <c r="H247" t="n">
         <v>0</v>
       </c>
+      <c r="I247" t="n">
+        <v>2</v>
+      </c>
+      <c r="J247" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="n">
@@ -7996,6 +9499,12 @@
       <c r="H248" t="n">
         <v>0</v>
       </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
@@ -8024,6 +9533,12 @@
       <c r="H249" t="n">
         <v>0</v>
       </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
@@ -8052,6 +9567,12 @@
       <c r="H250" t="n">
         <v>0</v>
       </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="n">
@@ -8080,6 +9601,12 @@
       <c r="H251" t="n">
         <v>0</v>
       </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="n">
@@ -8108,6 +9635,12 @@
       <c r="H252" t="n">
         <v>0</v>
       </c>
+      <c r="I252" t="n">
+        <v>1</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n">
@@ -8136,6 +9669,12 @@
       <c r="H253" t="n">
         <v>0</v>
       </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n">
@@ -8164,6 +9703,12 @@
       <c r="H254" t="n">
         <v>0</v>
       </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
@@ -8192,6 +9737,12 @@
       <c r="H255" t="n">
         <v>0</v>
       </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="n">
@@ -8220,6 +9771,12 @@
       <c r="H256" t="n">
         <v>0</v>
       </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -8248,6 +9805,12 @@
       <c r="H257" t="n">
         <v>6</v>
       </c>
+      <c r="I257" t="n">
+        <v>11</v>
+      </c>
+      <c r="J257" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n">
@@ -8276,6 +9839,12 @@
       <c r="H258" t="n">
         <v>0</v>
       </c>
+      <c r="I258" t="n">
+        <v>3</v>
+      </c>
+      <c r="J258" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
@@ -8304,6 +9873,12 @@
       <c r="H259" t="n">
         <v>2</v>
       </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n">
@@ -8332,6 +9907,12 @@
       <c r="H260" t="n">
         <v>3</v>
       </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
@@ -8360,6 +9941,12 @@
       <c r="H261" t="n">
         <v>0</v>
       </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n">
@@ -8388,6 +9975,12 @@
       <c r="H262" t="n">
         <v>1</v>
       </c>
+      <c r="I262" t="n">
+        <v>4</v>
+      </c>
+      <c r="J262" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
@@ -8416,6 +10009,12 @@
       <c r="H263" t="n">
         <v>0</v>
       </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n">
@@ -8444,6 +10043,12 @@
       <c r="H264" t="n">
         <v>1</v>
       </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
@@ -8472,6 +10077,12 @@
       <c r="H265" t="n">
         <v>1</v>
       </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n">
@@ -8500,6 +10111,12 @@
       <c r="H266" t="n">
         <v>0</v>
       </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n">
@@ -8528,6 +10145,12 @@
       <c r="H267" t="n">
         <v>7</v>
       </c>
+      <c r="I267" t="n">
+        <v>6</v>
+      </c>
+      <c r="J267" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n">
@@ -8556,6 +10179,12 @@
       <c r="H268" t="n">
         <v>1</v>
       </c>
+      <c r="I268" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n">
@@ -8584,6 +10213,12 @@
       <c r="H269" t="n">
         <v>2</v>
       </c>
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n">
@@ -8612,6 +10247,12 @@
       <c r="H270" t="n">
         <v>4</v>
       </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
@@ -8640,6 +10281,12 @@
       <c r="H271" t="n">
         <v>0</v>
       </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="n">
@@ -8668,6 +10315,12 @@
       <c r="H272" t="n">
         <v>3</v>
       </c>
+      <c r="I272" t="n">
+        <v>6</v>
+      </c>
+      <c r="J272" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n">
@@ -8696,6 +10349,12 @@
       <c r="H273" t="n">
         <v>0</v>
       </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="n">
@@ -8724,6 +10383,12 @@
       <c r="H274" t="n">
         <v>1</v>
       </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="n">
@@ -8752,6 +10417,12 @@
       <c r="H275" t="n">
         <v>0</v>
       </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n">
@@ -8780,6 +10451,12 @@
       <c r="H276" t="n">
         <v>0</v>
       </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n">
@@ -8808,6 +10485,12 @@
       <c r="H277" t="n">
         <v>0</v>
       </c>
+      <c r="I277" t="n">
+        <v>3</v>
+      </c>
+      <c r="J277" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="n">
@@ -8836,6 +10519,12 @@
       <c r="H278" t="n">
         <v>1</v>
       </c>
+      <c r="I278" t="n">
+        <v>3</v>
+      </c>
+      <c r="J278" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="n">
@@ -8864,6 +10553,12 @@
       <c r="H279" t="n">
         <v>0</v>
       </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="n">
@@ -8892,6 +10587,12 @@
       <c r="H280" t="n">
         <v>1</v>
       </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="n">
@@ -8920,6 +10621,12 @@
       <c r="H281" t="n">
         <v>0</v>
       </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="4" t="n">
@@ -8948,6 +10655,12 @@
       <c r="H282" t="n">
         <v>0</v>
       </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n">
@@ -8976,6 +10689,12 @@
       <c r="H283" t="n">
         <v>0</v>
       </c>
+      <c r="I283" t="n">
+        <v>3</v>
+      </c>
+      <c r="J283" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="n">
@@ -9004,6 +10723,12 @@
       <c r="H284" t="n">
         <v>0</v>
       </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n">
@@ -9032,6 +10757,12 @@
       <c r="H285" t="n">
         <v>0</v>
       </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="4" t="n">
@@ -9060,6 +10791,12 @@
       <c r="H286" t="n">
         <v>0</v>
       </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="n">
@@ -9088,6 +10825,12 @@
       <c r="H287" t="n">
         <v>0</v>
       </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
@@ -9116,6 +10859,12 @@
       <c r="H288" t="n">
         <v>0</v>
       </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n">
@@ -9144,6 +10893,12 @@
       <c r="H289" t="n">
         <v>0</v>
       </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="4" t="n">
@@ -9172,6 +10927,12 @@
       <c r="H290" t="n">
         <v>0</v>
       </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="4" t="n">
@@ -9200,6 +10961,12 @@
       <c r="H291" t="n">
         <v>0</v>
       </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="4" t="n">
@@ -9228,6 +10995,12 @@
       <c r="H292" t="n">
         <v>5</v>
       </c>
+      <c r="I292" t="n">
+        <v>6</v>
+      </c>
+      <c r="J292" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="n">
@@ -9256,6 +11029,12 @@
       <c r="H293" t="n">
         <v>3</v>
       </c>
+      <c r="I293" t="n">
+        <v>2</v>
+      </c>
+      <c r="J293" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="4" t="n">
@@ -9284,6 +11063,12 @@
       <c r="H294" t="n">
         <v>3</v>
       </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="4" t="n">
@@ -9312,6 +11097,12 @@
       <c r="H295" t="n">
         <v>5</v>
       </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="4" t="n">
@@ -9340,6 +11131,12 @@
       <c r="H296" t="n">
         <v>0</v>
       </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="4" t="n">
@@ -9368,6 +11165,12 @@
       <c r="H297" t="n">
         <v>4</v>
       </c>
+      <c r="I297" t="n">
+        <v>9</v>
+      </c>
+      <c r="J297" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="n">
@@ -9396,6 +11199,12 @@
       <c r="H298" t="n">
         <v>1</v>
       </c>
+      <c r="I298" t="n">
+        <v>1</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n">
@@ -9424,6 +11233,12 @@
       <c r="H299" t="n">
         <v>1</v>
       </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="4" t="n">
@@ -9452,6 +11267,12 @@
       <c r="H300" t="n">
         <v>0</v>
       </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n">
@@ -9480,6 +11301,12 @@
       <c r="H301" t="n">
         <v>0</v>
       </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="4" t="n">
@@ -9508,6 +11335,12 @@
       <c r="H302" t="n">
         <v>4</v>
       </c>
+      <c r="I302" t="n">
+        <v>11</v>
+      </c>
+      <c r="J302" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="4" t="n">
@@ -9536,6 +11369,12 @@
       <c r="H303" t="n">
         <v>2</v>
       </c>
+      <c r="I303" t="n">
+        <v>3</v>
+      </c>
+      <c r="J303" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="4" t="n">
@@ -9564,6 +11403,12 @@
       <c r="H304" t="n">
         <v>1</v>
       </c>
+      <c r="I304" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="4" t="n">
@@ -9592,6 +11437,12 @@
       <c r="H305" t="n">
         <v>3</v>
       </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="4" t="n">
@@ -9620,6 +11471,12 @@
       <c r="H306" t="n">
         <v>0</v>
       </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="n">
@@ -9648,6 +11505,12 @@
       <c r="H307" t="n">
         <v>2</v>
       </c>
+      <c r="I307" t="n">
+        <v>7</v>
+      </c>
+      <c r="J307" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="4" t="n">
@@ -9676,6 +11539,12 @@
       <c r="H308" t="n">
         <v>0</v>
       </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="4" t="n">
@@ -9704,6 +11573,12 @@
       <c r="H309" t="n">
         <v>2</v>
       </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="n">
@@ -9732,6 +11607,12 @@
       <c r="H310" t="n">
         <v>2</v>
       </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="4" t="n">
@@ -9760,6 +11641,12 @@
       <c r="H311" t="n">
         <v>0</v>
       </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="4" t="n">
@@ -9788,6 +11675,12 @@
       <c r="H312" t="n">
         <v>1</v>
       </c>
+      <c r="I312" t="n">
+        <v>5</v>
+      </c>
+      <c r="J312" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="4" t="n">
@@ -9816,6 +11709,12 @@
       <c r="H313" t="n">
         <v>1</v>
       </c>
+      <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="4" t="n">
@@ -9844,6 +11743,12 @@
       <c r="H314" t="n">
         <v>0</v>
       </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="4" t="n">
@@ -9872,6 +11777,12 @@
       <c r="H315" t="n">
         <v>0</v>
       </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="4" t="n">
@@ -9900,6 +11811,12 @@
       <c r="H316" t="n">
         <v>0</v>
       </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="4" t="n">
@@ -9928,6 +11845,12 @@
       <c r="H317" t="n">
         <v>0</v>
       </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="4" t="n">
@@ -9956,6 +11879,12 @@
       <c r="H318" t="n">
         <v>0</v>
       </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="4" t="n">
@@ -9984,6 +11913,12 @@
       <c r="H319" t="n">
         <v>0</v>
       </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="4" t="n">
@@ -10012,6 +11947,12 @@
       <c r="H320" t="n">
         <v>0</v>
       </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="4" t="n">
@@ -10040,6 +11981,12 @@
       <c r="H321" t="n">
         <v>0</v>
       </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="4" t="n">
@@ -10068,6 +12015,12 @@
       <c r="H322" t="n">
         <v>0</v>
       </c>
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="4" t="n">
@@ -10096,6 +12049,12 @@
       <c r="H323" t="n">
         <v>0</v>
       </c>
+      <c r="I323" t="n">
+        <v>2</v>
+      </c>
+      <c r="J323" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="4" t="n">
@@ -10124,6 +12083,12 @@
       <c r="H324" t="n">
         <v>0</v>
       </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="4" t="n">
@@ -10152,6 +12117,12 @@
       <c r="H325" t="n">
         <v>0</v>
       </c>
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="4" t="n">
@@ -10180,6 +12151,12 @@
       <c r="H326" t="n">
         <v>0</v>
       </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="4" t="n">
@@ -10208,6 +12185,12 @@
       <c r="H327" t="n">
         <v>6</v>
       </c>
+      <c r="I327" t="n">
+        <v>7</v>
+      </c>
+      <c r="J327" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="4" t="n">
@@ -10236,6 +12219,12 @@
       <c r="H328" t="n">
         <v>0</v>
       </c>
+      <c r="I328" t="n">
+        <v>2</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="4" t="n">
@@ -10264,6 +12253,12 @@
       <c r="H329" t="n">
         <v>4</v>
       </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="4" t="n">
@@ -10292,6 +12287,12 @@
       <c r="H330" t="n">
         <v>6</v>
       </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="4" t="n">
@@ -10320,6 +12321,12 @@
       <c r="H331" t="n">
         <v>0</v>
       </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="n">
@@ -10348,6 +12355,12 @@
       <c r="H332" t="n">
         <v>1</v>
       </c>
+      <c r="I332" t="n">
+        <v>3</v>
+      </c>
+      <c r="J332" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="4" t="n">
@@ -10376,6 +12389,12 @@
       <c r="H333" t="n">
         <v>0</v>
       </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="n">
@@ -10404,6 +12423,12 @@
       <c r="H334" t="n">
         <v>2</v>
       </c>
+      <c r="I334" t="n">
+        <v>1</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="n">
@@ -10432,6 +12457,12 @@
       <c r="H335" t="n">
         <v>4</v>
       </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="n">
@@ -10460,6 +12491,12 @@
       <c r="H336" t="n">
         <v>0</v>
       </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="4" t="n">
@@ -10488,6 +12525,12 @@
       <c r="H337" t="n">
         <v>1</v>
       </c>
+      <c r="I337" t="n">
+        <v>4</v>
+      </c>
+      <c r="J337" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="4" t="n">
@@ -10516,6 +12559,12 @@
       <c r="H338" t="n">
         <v>0</v>
       </c>
+      <c r="I338" t="n">
+        <v>1</v>
+      </c>
+      <c r="J338" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="4" t="n">
@@ -10544,6 +12593,12 @@
       <c r="H339" t="n">
         <v>3</v>
       </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="4" t="n">
@@ -10572,6 +12627,12 @@
       <c r="H340" t="n">
         <v>1</v>
       </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="4" t="n">
@@ -10600,6 +12661,12 @@
       <c r="H341" t="n">
         <v>0</v>
       </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="4" t="n">
@@ -10628,6 +12695,12 @@
       <c r="H342" t="n">
         <v>4</v>
       </c>
+      <c r="I342" t="n">
+        <v>8</v>
+      </c>
+      <c r="J342" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="4" t="n">
@@ -10656,6 +12729,12 @@
       <c r="H343" t="n">
         <v>1</v>
       </c>
+      <c r="I343" t="n">
+        <v>2</v>
+      </c>
+      <c r="J343" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="4" t="n">
@@ -10684,6 +12763,12 @@
       <c r="H344" t="n">
         <v>1</v>
       </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="4" t="n">
@@ -10712,6 +12797,12 @@
       <c r="H345" t="n">
         <v>1</v>
       </c>
+      <c r="I345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J345" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="4" t="n">
@@ -10740,6 +12831,12 @@
       <c r="H346" t="n">
         <v>0</v>
       </c>
+      <c r="I346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J346" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="4" t="n">
@@ -10768,6 +12865,12 @@
       <c r="H347" t="n">
         <v>2</v>
       </c>
+      <c r="I347" t="n">
+        <v>7</v>
+      </c>
+      <c r="J347" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="4" t="n">
@@ -10796,6 +12899,12 @@
       <c r="H348" t="n">
         <v>1</v>
       </c>
+      <c r="I348" t="n">
+        <v>1</v>
+      </c>
+      <c r="J348" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="4" t="n">
@@ -10824,6 +12933,12 @@
       <c r="H349" t="n">
         <v>0</v>
       </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="4" t="n">
@@ -10852,6 +12967,12 @@
       <c r="H350" t="n">
         <v>2</v>
       </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="4" t="n">
@@ -10880,6 +13001,12 @@
       <c r="H351" t="n">
         <v>0</v>
       </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="4" t="n">
@@ -10908,6 +13035,12 @@
       <c r="H352" t="n">
         <v>0</v>
       </c>
+      <c r="I352" t="n">
+        <v>2</v>
+      </c>
+      <c r="J352" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="4" t="n">
@@ -10936,6 +13069,12 @@
       <c r="H353" t="n">
         <v>0</v>
       </c>
+      <c r="I353" t="n">
+        <v>1</v>
+      </c>
+      <c r="J353" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="4" t="n">
@@ -10964,6 +13103,12 @@
       <c r="H354" t="n">
         <v>0</v>
       </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="4" t="n">
@@ -10992,6 +13137,12 @@
       <c r="H355" t="n">
         <v>0</v>
       </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="4" t="n">
@@ -11020,6 +13171,12 @@
       <c r="H356" t="n">
         <v>0</v>
       </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="4" t="n">
@@ -11048,6 +13205,12 @@
       <c r="H357" t="n">
         <v>0</v>
       </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="4" t="n">
@@ -11076,6 +13239,12 @@
       <c r="H358" t="n">
         <v>0</v>
       </c>
+      <c r="I358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="4" t="n">
@@ -11104,6 +13273,12 @@
       <c r="H359" t="n">
         <v>0</v>
       </c>
+      <c r="I359" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="4" t="n">
@@ -11132,6 +13307,12 @@
       <c r="H360" t="n">
         <v>0</v>
       </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="4" t="n">
@@ -11160,6 +13341,12 @@
       <c r="H361" t="n">
         <v>0</v>
       </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="4" t="n">
@@ -11188,6 +13375,12 @@
       <c r="H362" t="n">
         <v>3</v>
       </c>
+      <c r="I362" t="n">
+        <v>13</v>
+      </c>
+      <c r="J362" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="4" t="n">
@@ -11216,6 +13409,12 @@
       <c r="H363" t="n">
         <v>0</v>
       </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="4" t="n">
@@ -11244,6 +13443,12 @@
       <c r="H364" t="n">
         <v>4</v>
       </c>
+      <c r="I364" t="n">
+        <v>1</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="4" t="n">
@@ -11272,6 +13477,12 @@
       <c r="H365" t="n">
         <v>2</v>
       </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="4" t="n">
@@ -11300,6 +13511,12 @@
       <c r="H366" t="n">
         <v>0</v>
       </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="4" t="n">
@@ -11328,6 +13545,12 @@
       <c r="H367" t="n">
         <v>8</v>
       </c>
+      <c r="I367" t="n">
+        <v>9</v>
+      </c>
+      <c r="J367" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="4" t="n">
@@ -11356,6 +13579,12 @@
       <c r="H368" t="n">
         <v>0</v>
       </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="4" t="n">
@@ -11384,6 +13613,12 @@
       <c r="H369" t="n">
         <v>1</v>
       </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="4" t="n">
@@ -11412,6 +13647,12 @@
       <c r="H370" t="n">
         <v>1</v>
       </c>
+      <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="4" t="n">
@@ -11440,6 +13681,12 @@
       <c r="H371" t="n">
         <v>0</v>
       </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="4" t="n">
@@ -11468,6 +13715,12 @@
       <c r="H372" t="n">
         <v>3</v>
       </c>
+      <c r="I372" t="n">
+        <v>10</v>
+      </c>
+      <c r="J372" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="4" t="n">
@@ -11496,6 +13749,12 @@
       <c r="H373" t="n">
         <v>0</v>
       </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="4" t="n">
@@ -11524,6 +13783,12 @@
       <c r="H374" t="n">
         <v>2</v>
       </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="4" t="n">
@@ -11552,6 +13817,12 @@
       <c r="H375" t="n">
         <v>1</v>
       </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="4" t="n">
@@ -11580,6 +13851,12 @@
       <c r="H376" t="n">
         <v>0</v>
       </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="4" t="n">
@@ -11608,6 +13885,12 @@
       <c r="H377" t="n">
         <v>5</v>
       </c>
+      <c r="I377" t="n">
+        <v>9</v>
+      </c>
+      <c r="J377" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="4" t="n">
@@ -11636,6 +13919,12 @@
       <c r="H378" t="n">
         <v>0</v>
       </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="4" t="n">
@@ -11664,6 +13953,12 @@
       <c r="H379" t="n">
         <v>1</v>
       </c>
+      <c r="I379" t="n">
+        <v>1</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="4" t="n">
@@ -11692,6 +13987,12 @@
       <c r="H380" t="n">
         <v>0</v>
       </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="4" t="n">
@@ -11720,6 +14021,12 @@
       <c r="H381" t="n">
         <v>0</v>
       </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="4" t="n">
@@ -11748,6 +14055,12 @@
       <c r="H382" t="n">
         <v>5</v>
       </c>
+      <c r="I382" t="n">
+        <v>6</v>
+      </c>
+      <c r="J382" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="4" t="n">
@@ -11776,6 +14089,12 @@
       <c r="H383" t="n">
         <v>0</v>
       </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="4" t="n">
@@ -11804,6 +14123,12 @@
       <c r="H384" t="n">
         <v>5</v>
       </c>
+      <c r="I384" t="n">
+        <v>3</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="4" t="n">
@@ -11832,6 +14157,12 @@
       <c r="H385" t="n">
         <v>2</v>
       </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="4" t="n">
@@ -11860,6 +14191,12 @@
       <c r="H386" t="n">
         <v>0</v>
       </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="4" t="n">
@@ -11888,6 +14225,12 @@
       <c r="H387" t="n">
         <v>0</v>
       </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="4" t="n">
@@ -11916,6 +14259,12 @@
       <c r="H388" t="n">
         <v>0</v>
       </c>
+      <c r="I388" t="n">
+        <v>1</v>
+      </c>
+      <c r="J388" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="4" t="n">
@@ -11944,6 +14293,12 @@
       <c r="H389" t="n">
         <v>0</v>
       </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="4" t="n">
@@ -11972,6 +14327,12 @@
       <c r="H390" t="n">
         <v>0</v>
       </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="4" t="n">
@@ -12000,6 +14361,12 @@
       <c r="H391" t="n">
         <v>0</v>
       </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="4" t="n">
@@ -12028,6 +14395,12 @@
       <c r="H392" t="n">
         <v>0</v>
       </c>
+      <c r="I392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="4" t="n">
@@ -12056,6 +14429,12 @@
       <c r="H393" t="n">
         <v>0</v>
       </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="4" t="n">
@@ -12084,6 +14463,12 @@
       <c r="H394" t="n">
         <v>0</v>
       </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="4" t="n">
@@ -12112,6 +14497,12 @@
       <c r="H395" t="n">
         <v>0</v>
       </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="4" t="n">
@@ -12140,6 +14531,12 @@
       <c r="H396" t="n">
         <v>0</v>
       </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="4" t="n">
@@ -12168,6 +14565,12 @@
       <c r="H397" t="n">
         <v>8</v>
       </c>
+      <c r="I397" t="n">
+        <v>5</v>
+      </c>
+      <c r="J397" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="4" t="n">
@@ -12196,6 +14599,12 @@
       <c r="H398" t="n">
         <v>1</v>
       </c>
+      <c r="I398" t="n">
+        <v>3</v>
+      </c>
+      <c r="J398" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="4" t="n">
@@ -12224,6 +14633,12 @@
       <c r="H399" t="n">
         <v>0</v>
       </c>
+      <c r="I399" t="n">
+        <v>1</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="4" t="n">
@@ -12252,6 +14667,12 @@
       <c r="H400" t="n">
         <v>1</v>
       </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="4" t="n">
@@ -12278,6 +14699,12 @@
         <v>0</v>
       </c>
       <c r="H401" t="n">
+        <v>0</v>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12648,7 +15075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -12699,6 +15126,13 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
+          <t>Режим B7: «Наш» — конверсии и звонки по нашему правилу 60 дней из выгрузки CRM; «Как у клиента» — звонки: первый звонок номера за всю историю Ringostat (входящие, отслеживаемые каналы), формы: сеансы GA4 form_submit по источнику сеанса (google / cpc → Google Ads, facebook* → Facebook, остальное → Нет метки); подтверждено на двух периодах скринов клиента 2026-10-20. Продажи в обоих режимах одинаковые (наше правило).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
           <t>Период выбирается в ячейке B2 листа «Дашборд»; для «Свой период» даты вводятся в E3 и E4. «Текущий месяц» и «Текущая неделя» считаются от сегодняшней даты, но данных нет позже даты, указанной в B6 (данные обновляются повторным запуском скрипта profimet_sources_dashboard.py).</t>
         </is>
       </c>
